--- a/Outputs/test_original_predictions.xlsx
+++ b/Outputs/test_original_predictions.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>label</t>
+          <t>predicted_label</t>
         </is>
       </c>
     </row>
